--- a/relatorios/operacoes_2026-06-15.xlsx
+++ b/relatorios/operacoes_2026-06-15.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet name="Operações 15-06-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operações 15-06-2026'!$A$1:$Q$41</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,19 +31,12 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
-      <color rgb="00006100"/>
-    </font>
-    <font>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -57,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
-        <bgColor rgb="002F5496"/>
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,16 +77,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,26 +454,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:X82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="22" max="22"/>
+    <col width="42" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,29 +491,29 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Símbolo</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Direção</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Estratégia</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Timeframe</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Entrada</t>
@@ -531,42 +531,77 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Ticket Entrada</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Saída</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Preço Saída</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Motivo</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Ticket Saída</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Motivo Saída</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>SL Saída</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>PnL Bruto</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Taxas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Swap</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PnL Líquido</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Multiplicador</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Sinal</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Notas</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Criado em</t>
         </is>
       </c>
     </row>
@@ -581,21 +616,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -605,37 +640,65 @@
       <c r="H2" s="2" t="n">
         <v>336880</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>337560</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>2456613250</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>2026-06-15 10:08:58</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>337600</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>-1440</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="S2" s="3" t="n">
         <v>-1442.4</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 522.86, "rsi": 99.0, "sl_pts": 68000}</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-7.20. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2026-06-15 09:54:05</t>
         </is>
       </c>
     </row>
@@ -650,21 +713,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>EMA_PULLBACK</t>
         </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -674,37 +737,65 @@
       <c r="H3" s="2" t="n">
         <v>5059</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>5041.775</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>2456614170</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>2026-06-15 10:32:34</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>5048.5</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>-10.5</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="S3" s="3" t="n">
         <v>-11.7</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 13.25, "rsi": 63.9, "sl_pts": 17225}</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.01. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-06-15 09:55:25</t>
         </is>
       </c>
     </row>
@@ -719,21 +810,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -743,37 +834,65 @@
       <c r="H4" s="2" t="n">
         <v>7529.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="2" t="n">
         <v>7517.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>2456617050</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>2026-06-15 10:04:18</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>7529.5</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>-1.2</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 8.41, "rsi": 16.7, "sl_pts": 1200}</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-06-15 09:56:17</t>
         </is>
       </c>
     </row>
@@ -788,21 +907,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>STRONG_TREND</t>
         </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -812,37 +931,65 @@
       <c r="H5" s="2" t="n">
         <v>7529</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="2" t="n">
         <v>7557</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>2456633915</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>2026-06-15 10:04:22</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>7530</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="S5" s="3" t="n">
         <v>-2.2</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>{"strategy": "STRONG_TREND", "atr": 28.59, "rsi": 50.7, "sl_pts": 2800}</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.01. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-06-15 10:03:21</t>
         </is>
       </c>
     </row>
@@ -857,21 +1004,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>EMA_PULLBACK</t>
         </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -881,37 +1028,65 @@
       <c r="H6" s="2" t="n">
         <v>5053</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="2" t="n">
         <v>5029.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>2456748013</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>2026-06-15 11:41:37</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>5068.5</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="P6" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="S6" s="4" t="n">
         <v>14.3</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 19.57, "rsi": 57.8, "sl_pts": 23500}</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.02. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-06-15 10:39:02</t>
         </is>
       </c>
     </row>
@@ -926,21 +1101,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>STRONG_TREND</t>
         </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -950,37 +1125,65 @@
       <c r="H7" s="2" t="n">
         <v>7550</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="2" t="n">
         <v>7592</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>2456751264</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>2026-06-15 11:03:35</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>7553</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="S7" s="3" t="n">
         <v>-4.2</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>{"strategy": "STRONG_TREND", "atr": 33.43, "rsi": 33.0, "sl_pts": 4200}</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.03. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-06-15 10:40:05</t>
         </is>
       </c>
     </row>
@@ -995,21 +1198,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1019,37 +1222,65 @@
       <c r="H8" s="2" t="n">
         <v>336300</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="2" t="n">
         <v>336717</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>2456771322</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>2026-06-15 10:48:34</t>
         </is>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>336300</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="S8" s="3" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 417.14, "rsi": 71.9, "sl_pts": 41700}</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-06-15 10:47:41</t>
         </is>
       </c>
     </row>
@@ -1064,21 +1295,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1088,37 +1319,65 @@
       <c r="H9" s="2" t="n">
         <v>336300</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="2" t="n">
         <v>336754.28</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>2456794452</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>2026-06-15 11:00:40</t>
         </is>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>335920</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>760</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>757.6</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 378.57, "rsi": 77.8, "sl_pts": 45428}</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$3.80. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-06-15 10:57:23</t>
         </is>
       </c>
     </row>
@@ -1133,21 +1392,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>VWAP</t>
         </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1157,37 +1416,65 @@
       <c r="H10" s="2" t="n">
         <v>7550.25</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="2" t="n">
         <v>7499.25</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>2456803285</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>2026-06-15 11:03:42</t>
         </is>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="L10" s="2" t="n">
         <v>7552.75</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="P10" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>{"strategy": "VWAP", "atr": 64.02, "rsi": 41.5, "sl_pts": 5100, "vwap": 7416.01, "regime": "TREND_UP", "ema_fast": 7424.0, "ema_slow": 7402.0, "threshold_buy": 7438.26, "threshold_sell": 7393.76}</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.03. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:02:47</t>
         </is>
       </c>
     </row>
@@ -1202,21 +1489,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>EMA_PULLBACK</t>
         </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1226,37 +1513,65 @@
       <c r="H11" s="2" t="n">
         <v>7548.75</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="2" t="n">
         <v>7557.45</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>2456820148</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>2026-06-15 12:00:13</t>
         </is>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>7560</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="P11" s="2" t="n">
         <v>-11.25</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="3" t="n">
+      <c r="S11" s="3" t="n">
         <v>-12.45</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 7.25, "rsi": 49.5, "sl_pts": 870}</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.11. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:11:26</t>
         </is>
       </c>
     </row>
@@ -1271,21 +1586,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>VWAP</t>
         </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1295,37 +1610,65 @@
       <c r="H12" s="2" t="n">
         <v>337060</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="2" t="n">
         <v>340837.14</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>2456843855</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>2026-06-15 11:19:59</t>
         </is>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="L12" s="2" t="n">
         <v>337300</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="P12" s="2" t="n">
         <v>-480</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="3" t="n">
+      <c r="S12" s="3" t="n">
         <v>-482.4</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>{"strategy": "VWAP", "atr": 3777.14, "rsi": 41.6, "sl_pts": 377714, "vwap": 323402.88, "regime": "TREND_DOWN", "ema_fast": 321182.0, "ema_slow": 322414.0, "threshold_buy": 326636.91, "threshold_sell": 320168.85}</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-2.40. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:19:10</t>
         </is>
       </c>
     </row>
@@ -1340,21 +1683,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1364,37 +1707,65 @@
       <c r="H13" s="2" t="n">
         <v>173290</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="2" t="n">
         <v>173490</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>2456852385</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>2026-06-15 11:41:43</t>
         </is>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="L13" s="2" t="n">
         <v>172735</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="P13" s="2" t="n">
         <v>555</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="Q13" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>553.8</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 62.86, "rsi": 70.6, "sl_pts": 200}</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$555.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:21:56</t>
         </is>
       </c>
     </row>
@@ -1409,21 +1780,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1433,37 +1804,65 @@
       <c r="H14" s="2" t="n">
         <v>172920</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="2" t="n">
         <v>172760</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>2456898727</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>2026-06-15 11:42:24</t>
         </is>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>172820</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>-20</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="Q14" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="n">
+      <c r="S14" s="3" t="n">
         <v>-21.2</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="T14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 199.64, "rsi": 14.4, "sl_pts": 160}</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-100.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:39:30</t>
         </is>
       </c>
     </row>
@@ -1478,21 +1877,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1502,37 +1901,65 @@
       <c r="H15" s="2" t="n">
         <v>5066.5</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="2" t="n">
         <v>5070.5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>2456909630</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>2026-06-15 11:45:35</t>
         </is>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="L15" s="2" t="n">
         <v>5063</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="P15" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="Q15" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O15" t="n">
+      <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="S15" s="4" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 5.18, "rsi": 70.1, "sl_pts": 4000}</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:41:32</t>
         </is>
       </c>
     </row>
@@ -1547,21 +1974,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1571,37 +1998,65 @@
       <c r="H16" s="2" t="n">
         <v>337540</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="2" t="n">
         <v>337040</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>2456913817</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>2026-06-15 11:52:09</t>
         </is>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>337340</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>-400</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="Q16" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="3" t="n">
+      <c r="S16" s="3" t="n">
         <v>-402.4</v>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 1590.0, "rsi": 9.5, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-2.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:45:29</t>
         </is>
       </c>
     </row>
@@ -1616,21 +2071,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1640,37 +2095,65 @@
       <c r="H17" s="2" t="n">
         <v>172785</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="2" t="n">
         <v>172467</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>2456919511</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>2026-06-15 11:56:16</t>
         </is>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>172490</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>-295</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="Q17" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="3" t="n">
+      <c r="S17" s="3" t="n">
         <v>-296.2</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 265.0, "rsi": 11.6, "sl_pts": 318}</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-295.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:46:36</t>
         </is>
       </c>
     </row>
@@ -1685,21 +2168,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>EMA_PULLBACK</t>
         </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1709,37 +2192,65 @@
       <c r="H18" s="2" t="n">
         <v>5063.5</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="2" t="n">
         <v>5039.329</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>2456925486</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>2026-06-15 12:26:23</t>
         </is>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>5073</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>9.5</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="Q18" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="S18" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 20.14, "rsi": 56.6, "sl_pts": 24171}</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.01. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:50:07</t>
         </is>
       </c>
     </row>
@@ -1754,21 +2265,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1778,37 +2289,65 @@
       <c r="H19" s="2" t="n">
         <v>337540</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="2" t="n">
         <v>338040</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>2456929105</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>2026-06-15 11:52:13</t>
         </is>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="L19" s="2" t="n">
         <v>337440</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="P19" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="O19" t="n">
+      <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="S19" s="4" t="n">
         <v>197.6</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 1580.0, "rsi": 78.4, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$1.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:51:11</t>
         </is>
       </c>
     </row>
@@ -1823,21 +2362,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1847,37 +2386,65 @@
       <c r="H20" s="2" t="n">
         <v>172545</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="2" t="n">
         <v>172285</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>2456945632</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>2026-06-15 12:44:50</t>
         </is>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="L20" s="2" t="n">
         <v>172530</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="P20" s="2" t="n">
         <v>-15</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="Q20" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O20" t="n">
+      <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="n">
+      <c r="S20" s="3" t="n">
         <v>-16.2</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 325.71, "rsi": 12.6, "sl_pts": 260}</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-15.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:59:25</t>
         </is>
       </c>
     </row>
@@ -1892,21 +2459,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1916,37 +2483,65 @@
       <c r="H21" s="2" t="n">
         <v>7560</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="2" t="n">
         <v>7576</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>2456946035</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>2026-06-15 12:09:22</t>
         </is>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="L21" s="2" t="n">
         <v>7565</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="P21" s="2" t="n">
         <v>-5</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="3" t="n">
+      <c r="S21" s="3" t="n">
         <v>-6.2</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 10.75, "rsi": 78.1, "sl_pts": 1600}</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.05. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:00:09</t>
         </is>
       </c>
     </row>
@@ -1961,21 +2556,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>VWAP</t>
         </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1985,37 +2580,65 @@
       <c r="H22" s="2" t="n">
         <v>337740</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="2" t="n">
         <v>338240</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>2456952190</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>2026-06-15 12:09:11</t>
         </is>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="L22" s="2" t="n">
         <v>338180</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>-880</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="Q22" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="O22" t="n">
+      <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="S22" s="3" t="n">
         <v>-882.4</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>{"strategy": "VWAP", "atr": 3610.0, "rsi": 28.3, "sl_pts": 50000, "vwap": 323578.29, "regime": "TREND_DOWN", "ema_fast": 321403.0, "ema_slow": 322668.0, "threshold_buy": 326814.07, "threshold_sell": 320342.5}</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-4.40. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:02:17</t>
         </is>
       </c>
     </row>
@@ -2030,21 +2653,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2054,37 +2677,65 @@
       <c r="H23" s="2" t="n">
         <v>172790</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="2" t="n">
         <v>172470</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>2456958669</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>2026-06-15 12:39:54</t>
         </is>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="L23" s="2" t="n">
         <v>172605</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M23" s="2" t="n">
+      <c r="P23" s="2" t="n">
         <v>-37</v>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="Q23" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O23" t="n">
+      <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="P23" s="3" t="n">
+      <c r="S23" s="3" t="n">
         <v>-38.2</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="T23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 396.07, "rsi": 14.3, "sl_pts": 320}</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-185.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:05:59</t>
         </is>
       </c>
     </row>
@@ -2099,21 +2750,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>VWAP</t>
         </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2123,37 +2774,65 @@
       <c r="H24" s="2" t="n">
         <v>7563.25</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="2" t="n">
         <v>7512.25</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>2456959332</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>2026-06-15 12:09:27</t>
         </is>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="L24" s="2" t="n">
         <v>7564.25</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" s="2" t="n">
+      <c r="P24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O24" t="n">
+      <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="n">
+      <c r="S24" s="3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>{"strategy": "VWAP", "atr": 64.96, "rsi": 65.4, "sl_pts": 5100, "vwap": 7385.19, "regime": "TREND_UP", "ema_fast": 7418.0, "ema_slow": 7397.0, "threshold_buy": 7407.34, "threshold_sell": 7363.03}</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.01. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:07:42</t>
         </is>
       </c>
     </row>
@@ -2168,21 +2847,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2192,37 +2871,65 @@
       <c r="H25" s="2" t="n">
         <v>337960</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="2" t="n">
         <v>337460</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>2456961785</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>2026-06-15 12:10:06</t>
         </is>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="L25" s="2" t="n">
         <v>337940</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="P25" s="2" t="n">
         <v>-40</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="Q25" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="O25" t="n">
+      <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="P25" s="3" t="n">
+      <c r="S25" s="3" t="n">
         <v>-42.4</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 1671.43, "rsi": 9.7, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.20. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:09:06</t>
         </is>
       </c>
     </row>
@@ -2237,21 +2944,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2261,37 +2968,65 @@
       <c r="H26" s="2" t="n">
         <v>7564.25</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" s="2" t="n">
         <v>7549.25</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>2456968102</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>2026-06-15 12:23:05</t>
         </is>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="L26" s="2" t="n">
         <v>7565.5</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="P26" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="Q26" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O26" t="n">
+      <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="S26" s="4" t="n">
         <v>0.05000000000000004</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 10.64, "rsi": 3.1, "sl_pts": 1500}</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.01. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:15:02</t>
         </is>
       </c>
     </row>
@@ -2306,21 +3041,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2330,37 +3065,65 @@
       <c r="H27" s="2" t="n">
         <v>337720</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="2" t="n">
         <v>337220</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>2456969936</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>2026-06-15 13:01:54</t>
         </is>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="L27" s="2" t="n">
         <v>341220</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n">
+      <c r="P27" s="2" t="n">
         <v>7000</v>
       </c>
-      <c r="N27" s="2" t="n">
+      <c r="Q27" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="O27" t="n">
+      <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="S27" s="4" t="n">
         <v>6997.6</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 1692.86, "rsi": 5.9, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$35.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:17:41</t>
         </is>
       </c>
     </row>
@@ -2375,21 +3138,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>STRONG_TREND</t>
         </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2399,37 +3162,65 @@
       <c r="H28" s="2" t="n">
         <v>7566.25</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="2" t="n">
         <v>7604.25</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>2456976521</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>2026-06-15 12:23:09</t>
         </is>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="L28" s="2" t="n">
         <v>7566.5</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n">
+      <c r="P28" s="2" t="n">
         <v>-0.25</v>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="Q28" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="P28" s="3" t="n">
+      <c r="S28" s="3" t="n">
         <v>-1.45</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>{"strategy": "STRONG_TREND", "atr": 38.12, "rsi": 42.1, "sl_pts": 3800}</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:22:15</t>
         </is>
       </c>
     </row>
@@ -2444,21 +3235,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2468,37 +3259,65 @@
       <c r="H29" s="2" t="n">
         <v>5071</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="2" t="n">
         <v>5078</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>2456986889</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>2026-06-15 12:27:18</t>
         </is>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="L29" s="2" t="n">
         <v>5072</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="P29" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="Q29" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O29" t="n">
+      <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="n">
+      <c r="S29" s="3" t="n">
         <v>-2.2</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 9.18, "rsi": 71.8, "sl_pts": 7000}</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:26:18</t>
         </is>
       </c>
     </row>
@@ -2513,21 +3332,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2537,37 +3356,65 @@
       <c r="H30" s="2" t="n">
         <v>7568</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="2" t="n">
         <v>7554</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>2456991673</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>2026-06-15 12:48:15</t>
         </is>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="L30" s="2" t="n">
         <v>7574.5</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M30" s="2" t="n">
+      <c r="P30" s="2" t="n">
         <v>6.5</v>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="Q30" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O30" t="n">
+      <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="S30" s="4" t="n">
         <v>5.3</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 11.02, "rsi": 7.2, "sl_pts": 1400}</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.07. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:30:24</t>
         </is>
       </c>
     </row>
@@ -2582,21 +3429,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>EMA_PULLBACK</t>
         </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2606,37 +3453,65 @@
       <c r="H31" s="2" t="n">
         <v>5070.5</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="2" t="n">
         <v>5060</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>2456996862</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>2026-06-15 12:56:29</t>
         </is>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="L31" s="2" t="n">
         <v>5076</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M31" s="2" t="n">
+      <c r="P31" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="N31" s="2" t="n">
+      <c r="Q31" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O31" t="n">
+      <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="S31" s="4" t="n">
         <v>4.3</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 8.32, "rsi": 64.7, "sl_pts": 10500}</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.01. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:34:13</t>
         </is>
       </c>
     </row>
@@ -2651,21 +3526,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2675,37 +3550,65 @@
       <c r="H32" s="2" t="n">
         <v>172605</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="2" t="n">
         <v>172005</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>2457005734</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>2026-06-15 13:16:43</t>
         </is>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="L32" s="2" t="n">
         <v>172255</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n">
+      <c r="P32" s="2" t="n">
         <v>-70</v>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="Q32" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O32" t="n">
+      <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="n">
+      <c r="S32" s="3" t="n">
         <v>-71.2</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="T32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 447.14, "rsi": 24.9, "sl_pts": 600}</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-350.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:42:09</t>
         </is>
       </c>
     </row>
@@ -2720,21 +3623,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2744,37 +3647,65 @@
       <c r="H33" s="2" t="n">
         <v>172550</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="2" t="n">
         <v>172200</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>2457010669</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>2026-06-15 13:18:55</t>
         </is>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="L33" s="2" t="n">
         <v>172220</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M33" s="2" t="n">
+      <c r="P33" s="2" t="n">
         <v>-330</v>
       </c>
-      <c r="N33" s="2" t="n">
+      <c r="Q33" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O33" t="n">
+      <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="P33" s="3" t="n">
+      <c r="S33" s="3" t="n">
         <v>-331.2</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 400.71, "rsi": 28.6, "sl_pts": 350}</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-330.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:46:23</t>
         </is>
       </c>
     </row>
@@ -2789,21 +3720,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>STRONG_TREND</t>
         </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2813,37 +3744,65 @@
       <c r="H34" s="2" t="n">
         <v>7573</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="2" t="n">
         <v>7606</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>2457012009</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>2026-06-15 12:48:19</t>
         </is>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="L34" s="2" t="n">
         <v>7575</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n">
+      <c r="P34" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="Q34" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O34" t="n">
+      <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="P34" s="3" t="n">
+      <c r="S34" s="3" t="n">
         <v>-3.2</v>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>{"strategy": "STRONG_TREND", "atr": 33.68, "rsi": 33.8, "sl_pts": 3300}</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.02. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:47:24</t>
         </is>
       </c>
     </row>
@@ -2858,21 +3817,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2882,37 +3841,65 @@
       <c r="H35" s="2" t="n">
         <v>5075.5</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" s="2" t="n">
         <v>5080.5</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>2457023368</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>2026-06-15 12:57:25</t>
         </is>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="L35" s="2" t="n">
         <v>5076.5</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M35" s="2" t="n">
+      <c r="P35" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="Q35" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O35" t="n">
+      <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="P35" s="3" t="n">
+      <c r="S35" s="3" t="n">
         <v>-2.2</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 7.04, "rsi": 79.5, "sl_pts": 5000}</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:56:25</t>
         </is>
       </c>
     </row>
@@ -2927,21 +3914,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>STRONG_TREND</t>
         </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2951,37 +3938,65 @@
       <c r="H36" s="2" t="n">
         <v>7579.25</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" s="2" t="n">
         <v>7610.25</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>2457032006</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>2026-06-15 13:09:39</t>
         </is>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="L36" s="2" t="n">
         <v>7580.5</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M36" s="2" t="n">
+      <c r="P36" s="2" t="n">
         <v>-1.25</v>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="Q36" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O36" t="n">
+      <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="P36" s="3" t="n">
+      <c r="S36" s="3" t="n">
         <v>-2.45</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>{"strategy": "STRONG_TREND", "atr": 31.41, "rsi": 51.2, "sl_pts": 3100}</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.01. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:00:20</t>
         </is>
       </c>
     </row>
@@ -2996,21 +4011,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3020,37 +4035,65 @@
       <c r="H37" s="2" t="n">
         <v>5073.5</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="2" t="n">
         <v>5081.385</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>2457041485</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>2026-06-15 13:19:43</t>
         </is>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="L37" s="2" t="n">
         <v>5084.5</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M37" s="2" t="n">
+      <c r="P37" s="2" t="n">
         <v>-11</v>
       </c>
-      <c r="N37" s="2" t="n">
+      <c r="Q37" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O37" t="n">
+      <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="P37" s="3" t="n">
+      <c r="S37" s="3" t="n">
         <v>-12.2</v>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 6.57, "rsi": 77.9, "sl_pts": 7885}</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.01. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:08:10</t>
         </is>
       </c>
     </row>
@@ -3065,21 +4108,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3089,37 +4132,65 @@
       <c r="H38" s="2" t="n">
         <v>7581</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="2" t="n">
         <v>7575</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>2457043546</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>2026-06-15 13:13:03</t>
         </is>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="L38" s="2" t="n">
         <v>7580.25</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n">
+      <c r="P38" s="2" t="n">
         <v>-0.75</v>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="Q38" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="P38" s="3" t="n">
+      <c r="S38" s="3" t="n">
         <v>-1.95</v>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 4.05, "rsi": 23.5, "sl_pts": 600}</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.01. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:09:36</t>
         </is>
       </c>
     </row>
@@ -3134,21 +4205,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>RSI_REVERSION</t>
         </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3158,37 +4229,65 @@
       <c r="H39" s="2" t="n">
         <v>341560</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="2" t="n">
         <v>341060</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>2457045612</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>2026-06-15 13:33:17</t>
         </is>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="L39" s="2" t="n">
         <v>341600</v>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M39" s="2" t="n">
+      <c r="P39" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="N39" s="2" t="n">
+      <c r="Q39" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="O39" t="n">
+      <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="P39" s="4" t="n">
+      <c r="S39" s="4" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 1001.43, "rsi": 24.0, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.40. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:12:48</t>
         </is>
       </c>
     </row>
@@ -3203,21 +4302,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>BOLLINGER</t>
         </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3227,37 +4326,65 @@
       <c r="H40" s="2" t="n">
         <v>172440</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="2" t="n">
         <v>173095</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>2457050993</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>2026-06-15 13:19:35</t>
         </is>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="L40" s="2" t="n">
         <v>172025</v>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>SL_SERVIDOR</t>
         </is>
       </c>
-      <c r="M40" s="2" t="n">
+      <c r="P40" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="N40" s="2" t="n">
+      <c r="Q40" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O40" t="n">
+      <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="S40" s="4" t="n">
         <v>81.8</v>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="T40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>{"strategy": "BOLLINGER", "atr": 436.43, "rsi": 89.6, "sl_pts": 655, "bb_upper": 172216.12, "bb_mid": 171678.0, "bb_lower": 171139.88}</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
         <is>
           <t>Posição fechada pelo servidor MT5. PnL estimado: R$415.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:16:39</t>
         </is>
       </c>
     </row>
@@ -3272,21 +4399,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>BOLLINGER</t>
         </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3296,56 +4423,3015 @@
       <c r="H41" s="2" t="n">
         <v>172255</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="2" t="n">
         <v>172605</v>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="n">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2457055653</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:21:12</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>171710</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
+      <c r="S41" s="4" t="n">
+        <v>543.8</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>{"strategy": "BOLLINGER", "atr": 409.29, "rsi": 88.1, "sl_pts": 350, "bb_upper": 172222.14, "bb_mid": 171692.0, "bb_lower": 171161.86}</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$545.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:18:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>151</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BITM26</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>EMA_PULLBACK</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:55:57</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>341400</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>341900</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2457114518</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:14:08</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>340060</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>2680</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="O41" t="n">
+      <c r="S42" s="4" t="n">
+        <v>2677.6</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 1032.86, "rsi": 64.5, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$13.40. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:55:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>152</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>DOLN26</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>EMA_PULLBACK</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:56:47</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>5082</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>5075</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2457116948</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:28:20</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>5076.5</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="P41" t="n">
+      <c r="S43" s="3" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 5.96, "rsi": 56.1, "sl_pts": 7000}</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.01. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:56:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>153</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>WSPM26</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:57:29</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>7574.25</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>7562.25</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2457117454</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:11:48</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>7574</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="S44" s="3" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 8.18, "rsi": 14.0, "sl_pts": 1200}</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:57:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>154</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>WINM26</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:06:00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>171635</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>172128</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2457129506</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:35:00</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>171415</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="4" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 410.71, "rsi": 80.0, "sl_pts": 493}</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$220.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>155</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>WSPM26</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>STRONG_TREND</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:10:55</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>7571.25</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>7593.25</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2457134264</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:11:52</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>7574</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>{"strategy": "STRONG_TREND", "atr": 22.93, "rsi": 52.8, "sl_pts": 2200}</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.03. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:10:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>156</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BITM26</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>EMA_PULLBACK</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:16:10</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>340140</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>340640</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2457139141</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:35:04</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>339620</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="4" t="n">
+        <v>1037.6</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 1027.14, "rsi": 69.7, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$5.20. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:16:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>157</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>INDM26</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:21:52</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>171635</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>171985</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2457149933</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:35:14</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>171445</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="4" t="n">
+        <v>188.8</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 332.5, "rsi": 78.8, "sl_pts": 350}</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$190.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:21:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>158</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>DOLN26</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>EMA_PULLBACK</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:29:21</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>5077.5</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>5052.943</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2457157682</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:35:10</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>5081.5</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 18.89, "rsi": 47.0, "sl_pts": 24557}</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:29:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>159</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>WSPM26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>EMA_PULLBACK</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:36:02</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>7578.25</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>7588.57</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2457171846</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:03:30</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>7564.25</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 6.88, "rsi": 52.6, "sl_pts": 1032}</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.14. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:36:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>160</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>WINM26</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:37:10</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>171435</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>171840</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2457173602</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:10:37</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>170810</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="4" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 337.5, "rsi": 78.9, "sl_pts": 405}</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$625.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:37:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>161</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BITM26</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>EMA_PULLBACK</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:38:09</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>339820</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>340320</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2457174710</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:43:53</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>340320</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="n">
+        <v>-1002.4</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 967.14, "rsi": 60.6, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$-5.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:38:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>162</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>DOLN26</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>EMA_PULLBACK</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:39:16</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>5083</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>5074.585</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2457177403</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:32:02</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>5087.5</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 5.61, "rsi": 62.3, "sl_pts": 8415}</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:39:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>163</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>INDM26</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:40:00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>171325</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>171675</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2457178524</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:11:34</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>170845</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="4" t="n">
+        <v>478.8</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 319.64, "rsi": 78.9, "sl_pts": 350}</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$480.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:40:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>164</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BITM26</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>EMA_PULLBACK</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:51:20</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>340300</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>340800</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2457191862</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:01:36</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>339960</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>680</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="4" t="n">
+        <v>677.6</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 975.71, "rsi": 66.7, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$3.40. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:51:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>165</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BITM26</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:01:33</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>339860</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>339360</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2457201964</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:03:16</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>339800</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>-120</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="3" t="n">
+        <v>-122.4</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 728.57, "rsi": 18.4, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.60. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:01:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>166</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>WSPM26</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:02:37</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>7566.75</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>7509.75</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2457207924</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:03:32</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>7564.25</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>{"strategy": "VWAP", "atr": 71.73, "rsi": 62.0, "sl_pts": 5700, "vwap": 7369.45, "regime": "TREND_UP", "ema_fast": 7400.0, "ema_slow": 7384.0, "threshold_buy": 7391.56, "threshold_sell": 7347.34}</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.03. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:02:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>167</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BITM26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>EMA_PULLBACK</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:09:52</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>340020</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>340520</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2457226809</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:18:19</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>339900</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="4" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 974.29, "rsi": 69.4, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$1.20. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:09:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>168</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>WSPM26</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>STRONG_TREND</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:15:22</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>7568.25</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>7587.5</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2457233661</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:32:10</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>7565.5</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>{"strategy": "STRONG_TREND", "atr": 16.04, "rsi": 49.8, "sl_pts": 1925}</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.03. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:15:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>169</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BITM26</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:18:17</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>339940</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>339440</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2457236710</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:19:09</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>340020</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="4" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 880.0, "rsi": 8.8, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.80. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:18:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>170</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BITM26</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>EMA_PULLBACK</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:27:06</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>339940</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>340440</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2457245728</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:31:13</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>340020</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>-160</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>-162.4</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 907.14, "rsi": 65.4, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.80. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:27:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>171</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>DOLN26</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:31:57</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>5087</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>5081.5</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2457252531</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:09:13</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>5090</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 4.54, "rsi": 24.0, "sl_pts": 5500}</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$0.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:31:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>172</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BITM26</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:35:36</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>340480</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>339980</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2457260086</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:42:44</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>339960</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>-1040</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3" t="n">
+        <v>-1042.4</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 1015.71, "rsi": 22.5, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$-5.20. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:35:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>173</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>INDM26</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:41:12</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>170655</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>170865</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2457266641</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:56:26</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>170845</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>-190</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3" t="n">
+        <v>-191.2</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 148.57, "rsi": 72.8, "sl_pts": 210}</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$-190.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:41:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>174</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BITM26</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:44:30</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>339880</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>339380</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2457268964</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:18:51</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>339340</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>-1080</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3" t="n">
+        <v>-1082.4</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 1078.57, "rsi": 14.0, "sl_pts": 50000}</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$-5.40. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:44:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>175</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>WINM26</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:45:53</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>170720</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>170955</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2457270662</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:51:06</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>170715</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>eod</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>EOD_16:45</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 196.43, "rsi": 77.8, "sl_pts": 235}</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Fechamento obrigatório de intraday</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:45:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>176</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>WSPM26</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:51:34</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>7570.5</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>7563.5</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2457275099</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:12:43</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>7564.75</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="3" t="n">
+        <v>-6.95</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 4.91, "rsi": 22.0, "sl_pts": 700}</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$-0.06. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>177</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>INDM26</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:57:59</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>170825</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>171053</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2457280565</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:10:22</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>170710</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>SL_SERVIDOR</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="4" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 190.71, "rsi": 76.3, "sl_pts": 228}</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Posição fechada pelo servidor MT5. PnL estimado: R$115.00. Fees serão sincronizados no EOD.</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:57:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>178</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>DOLN26</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>EMA_PULLBACK</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:10:17</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>5090.5</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>5063.935</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2457295925</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:51:23</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>5084.5</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>eod</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>EOD_16:45</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>{"strategy": "EMA_PULLBACK", "atr": 17.71, "rsi": 55.5, "sl_pts": 26565}</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Fechamento obrigatório de intraday</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:10:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>179</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>INDM26</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>RSI_REVERSION</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:11:50</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>170665</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>170885</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2457297673</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:51:54</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>170700</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>eod</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>EOD_16:45</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>-35</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3" t="n">
+        <v>-36.2</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>FUTURE</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>{"strategy": "RSI_REVERSION", "atr": 182.86, "rsi": 77.8, "sl_pts": 220}</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Fechamento obrigatório de intraday</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>2026-06-15 16:11:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>RESUMO</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Total de Trades: 40</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Wins: 13 | Losses: 26 | Win Rate: 32.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>PnL Total: R$ +4,609.45</t>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Total trades:</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Fechados:</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>29W / 40L (42% WR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PnL Total:</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>R$ 7,241.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>POR ATIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BITM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>20 trades | 9W/11L (45%)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>R$ +6,152.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>WINM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>7 trades | 3W/4L (43%)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>R$ +117.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DOLN26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>13 trades | 7W/6L (54%)</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>R$ -5.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>INDM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>10 trades | 5W/5L (50%)</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>R$ +1,008.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>WSPM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>19 trades | 5W/14L (26%)</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>R$ -30.55</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>